--- a/docs/MindX•SDK•6.0.RC1•mxRec•公网地址和邮箱地址.xlsx
+++ b/docs/MindX•SDK•6.0.RC1•mxRec•公网地址和邮箱地址.xlsx
@@ -1,14 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\helin\mxRec工作目录\代码\mxrec\docs\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="17775" activeTab="2"/>
+    <workbookView windowHeight="17655" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -17,14 +13,27 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">WordSummary!$A$1:$F$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Detail_1!$A$1:$C$156</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Detail_1!$A$1:$C$161</definedName>
   </definedNames>
-  <calcPr/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="263">
   <si>
     <t>Scan Record ID</t>
   </si>
@@ -682,17 +691,160 @@
   <si>
     <t>["https://www.hiascend.com"]</t>
   </si>
+  <si>
+    <t>["https://github.com/pybind/pybind11/archive/refs/tags/v2.10.3.zip"]</t>
+  </si>
+  <si>
+    <t>["https://github.com/huaweicloud/huaweicloud-sdk-c-obs/archive/refs/tags/v3.23.9.zip"]</t>
+  </si>
+  <si>
+    <t>["https://download.open-mpi.org/release/open-mpi/v4.1/openmpi-4.1.5.tar.gz"]</t>
+  </si>
+  <si>
+    <t>["https://github.com/google/googletest/archive/refs/tags/release-1.8.1.zip"]</t>
+  </si>
+  <si>
+    <t>["https://github.com/ez8-co/emock/archive/refs/tags/v0.9.0.zip"]</t>
+  </si>
+  <si>
+    <t>mxrec/tools/model_convert/README.md</t>
+  </si>
+  <si>
+    <t>["https://www.tensorflow.org/guide/estimator?hl=zh-cn"]</t>
+  </si>
+  <si>
+    <t>mxrec/examples/ps_adapt_to_mxrec/ps_adapt_to_mxrec.md</t>
+  </si>
+  <si>
+    <t>["https://github.com/dmlc/ps-lite"]</t>
+  </si>
+  <si>
+    <t>["https://gitee.com/ascend/mxrec/tree/develop/"]</t>
+  </si>
+  <si>
+    <t>["https://github.com/dmlc/ps-lite.git"]</t>
+  </si>
+  <si>
+    <t>mxrec/examples/mmoe/README.md</t>
+  </si>
+  <si>
+    <t>["https://github.com/PaddlePaddle/PaddleRec/commit/54b6a96abae574a04c7fcac53df190f885970c3f"]</t>
+  </si>
+  <si>
+    <t>["https://github.com/PaddlePaddle/PaddleRec/tree/master/models/multitask/mmoe"]</t>
+  </si>
+  <si>
+    <t>["https://archive.ics.uci.edu/static/public/117/census+income+kdd.zip"]</t>
+  </si>
+  <si>
+    <t>mxrec/examples/WideDeep/README.md</t>
+  </si>
+  <si>
+    <t>["https://github.com/ZiyaoGeng/RecLearn/tree/4bbfb492b872c5a3290a2bce1ed5c160162558a3"]</t>
+  </si>
+  <si>
+    <t>["https://github.com/ZiyaoGeng/RecLearn"]</t>
+  </si>
+  <si>
+    <t>["https://ailab.criteo.com/ressources/kaggle-display-advertising-challenge-dataset.tar.gz"]</t>
+  </si>
+  <si>
+    <t>mxrec/examples/xDeepFM/README.md</t>
+  </si>
+  <si>
+    <t>["https://github.com/Leavingseason/xDeepFM"]</t>
+  </si>
+  <si>
+    <t>mxrec/examples/rec_infer/README.md</t>
+  </si>
+  <si>
+    <t>["https://github.com/tensorflow/serving/archive/1.15.0.zip"]</t>
+  </si>
+  <si>
+    <t>mxrec/examples/rec_infer/optimize/README.md</t>
+  </si>
+  <si>
+    <t>["https://github.com/ARM-software/optimized-routines/tree/v23.01"]</t>
+  </si>
+  <si>
+    <t>["https://github.com/jemalloc/jemalloc/archive/refs/tags/5.3.0.tar.gz"]</t>
+  </si>
+  <si>
+    <t>["https://grpc.github.io/grpc/cpp/classgrpc_1_1_server_builder.html"]</t>
+  </si>
+  <si>
+    <t>mxrec/examples/dlrm/criteo_tb/README.md</t>
+  </si>
+  <si>
+    <t>["https://labs.criteo.com/2013/12/download-terabyte-click-logs/"]</t>
+  </si>
+  <si>
+    <t>["https://storage.googleapis.com/criteo-cail-datasets/day_{`seq -s “,” 0 23`}.gz"]</t>
+  </si>
+  <si>
+    <t>mxrec/third_party/expected/README.md</t>
+  </si>
+  <si>
+    <t>["https://tl.tartanllama.xyz/en/latest/?badge=latest"]</t>
+  </si>
+  <si>
+    <t>["https://github.com/TartanLlama/expected/actions/workflows/cmake.yml"]</t>
+  </si>
+  <si>
+    <t>["https://ci.appveyor.com/project/TartanLlama/expected"]</t>
+  </si>
+  <si>
+    <t>["https://github.com/microsoft/vcpkg/tree/master/ports/tl-expected"]</t>
+  </si>
+  <si>
+    <t>["https://github.com/yipdw/conan-tl-expected"]</t>
+  </si>
+  <si>
+    <t>["http://www.open-std.org/jtc1/sc22/wg21/docs/papers/2017/p0323r3.pdf"]</t>
+  </si>
+  <si>
+    <t>["http://creativecommons.org/publicdomain/zero/1.0/"]</t>
+  </si>
+  <si>
+    <t>["https://twitter.com/TartanLlama"]</t>
+  </si>
+  <si>
+    <t>mxrec/third_party/expected/CMakeLists.txt</t>
+  </si>
+  <si>
+    <t>["https://tl.tartanllama.xyz"]</t>
+  </si>
+  <si>
+    <t>["https://github.com/catchorg/Catch2/archive/v2.13.10.zip"]</t>
+  </si>
+  <si>
+    <t>mxrec/third_party/expected/include/tl/expected.hpp</t>
+  </si>
+  <si>
+    <t>["http://tl.tartanllama.xyz/"]</t>
+  </si>
+  <si>
+    <t>["https://stackoverflow.com/questions/38288042/c11-14-invoke-workaround"]</t>
+  </si>
+  <si>
+    <t>["https://stackoverflow.com/questions/26744589/what-is-a-proper-way-to-implement-is-swappable-to-test-for-the-swappable-concept"]</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -705,6 +857,23 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -713,11 +882,156 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="微软雅黑"/>
+      <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -736,60 +1050,249 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
-    <border/>
+  <borders count="18">
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-    </border>
-    <border>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-    </border>
-    <border>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color auto="1"/>
       </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <right style="thin">
+      <left/>
+      <right/>
+      <top style="thin">
         <color auto="1"/>
-      </right>
+      </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color auto="1"/>
       </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-    </border>
-    <border>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -804,15 +1307,307 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -824,47 +1619,140 @@
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color theme="1"/>
@@ -888,46 +1776,21 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="double">
-          <color theme="4"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor theme="4" tint="0.799981688894314"/>
           <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <color theme="1"/>
+        <b val="1"/>
       </font>
       <fill>
         <patternFill patternType="solid">
@@ -943,7 +1806,58 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
         <color theme="1"/>
       </font>
       <fill>
@@ -963,50 +1877,9 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor theme="4" tint="0.799981688894314"/>
@@ -1021,28 +1894,33 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
-      <tableStyleElement type="wholeTable" dxfId="0"/>
-      <tableStyleElement type="headerRow" dxfId="1"/>
-      <tableStyleElement type="totalRow" dxfId="2"/>
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
       <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="3"/>
-      <tableStyleElement type="firstRowStripe" dxfId="4"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="4"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="6"/>
-      <tableStyleElement type="firstRowStripe" dxfId="4"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="4"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="7"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="3"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="8"/>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
       <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="10"/>
-      <tableStyleElement type="pageFieldValues" dxfId="11"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1051,10 +1929,10 @@
   <a:themeElements>
     <a:clrScheme name="WPS">
       <a:dk1>
-        <a:sysClr val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -1293,11 +2171,14 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="36.75" customWidth="1"/>
@@ -1310,201 +2191,204 @@
     <col min="9" max="9" width="14.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="15" spans="1:9">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2">
+    <row r="2" spans="1:9">
+      <c r="A2" s="8">
         <v>6284</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="3">
-        <v>45231.752569444398</v>
-      </c>
-      <c r="E2" s="3">
-        <v>45231.752766203703</v>
-      </c>
-      <c r="F2" s="2" t="b">
+      <c r="D2" s="9">
+        <v>45231.7525694444</v>
+      </c>
+      <c r="E2" s="9">
+        <v>45231.7527662037</v>
+      </c>
+      <c r="F2" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="8">
         <v>160</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2" s="8">
         <v>158</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2" s="8">
         <v>161</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:9">
+      <c r="A6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="6"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="7"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="9"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="7"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="9"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="7"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="9"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="7"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="9"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="7"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="9"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="9"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="9"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="7"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="9"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="7"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="9"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="10"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="12"/>
-    </row>
-    <row r="22">
-      <c r="G22" s="13"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="17"/>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="12"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="18"/>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="12"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="18"/>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="12"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="18"/>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="12"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="18"/>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="12"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="18"/>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="12"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="18"/>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="12"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="18"/>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="12"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="18"/>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="12"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="18"/>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="14"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="19"/>
+    </row>
+    <row r="22" spans="7:7">
+      <c r="G22" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A6:I16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="33.625" customWidth="1"/>
     <col min="2" max="2" width="10.375" customWidth="1"/>
@@ -1513,27 +2397,27 @@
     <col min="5" max="6" width="14.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15">
-      <c r="A1" s="14" t="s">
+    <row r="1" ht="15" spans="1:6">
+      <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -1553,7 +2437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -1573,7 +2457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -1594,1806 +2478,2198 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F4"/>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F4" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D197"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="108.5" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="133.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15">
-      <c r="A1" s="14" t="s">
+    <row r="1" ht="15" spans="1:4">
+      <c r="A1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="14"/>
-    </row>
-    <row r="2" ht="16.5">
-      <c r="A2" s="15" t="s">
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" ht="16.5" spans="1:3">
+      <c r="A2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="3" ht="16.5">
-      <c r="A3" s="15" t="s">
+    <row r="3" ht="16.5" spans="1:3">
+      <c r="A3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="4" ht="16.5">
-      <c r="A4" s="15" t="s">
+    <row r="4" ht="16.5" spans="1:3">
+      <c r="A4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" ht="16.5">
-      <c r="A5" s="15" t="s">
+    <row r="5" ht="16.5" spans="1:3">
+      <c r="A5" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="6" ht="16.5">
-      <c r="A6" s="15" t="s">
+    <row r="6" ht="16.5" spans="1:3">
+      <c r="A6" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="7" ht="16.5">
-      <c r="A7" s="15" t="s">
+    <row r="7" ht="16.5" spans="1:3">
+      <c r="A7" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="8" ht="16.5">
-      <c r="A8" s="15" t="s">
+    <row r="8" ht="16.5" spans="1:3">
+      <c r="A8" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="9" ht="16.5">
-      <c r="A9" s="15" t="s">
+    <row r="9" ht="16.5" spans="1:3">
+      <c r="A9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="10" ht="16.5">
-      <c r="A10" s="15" t="s">
+    <row r="10" ht="16.5" spans="1:3">
+      <c r="A10" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="11" ht="16.5">
-      <c r="A11" s="15" t="s">
+    <row r="11" ht="16.5" spans="1:3">
+      <c r="A11" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="12" ht="16.5">
-      <c r="A12" s="15" t="s">
+    <row r="12" ht="16.5" spans="1:3">
+      <c r="A12" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="15" t="s">
+      <c r="B12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="13" ht="16.5">
-      <c r="A13" s="15" t="s">
+    <row r="13" ht="16.5" spans="1:3">
+      <c r="A13" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="15" t="s">
+      <c r="B13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="14" ht="16.5">
-      <c r="A14" s="15" t="s">
+    <row r="14" ht="16.5" spans="1:3">
+      <c r="A14" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="15" t="s">
+      <c r="B14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="15" ht="16.5">
-      <c r="A15" s="15" t="s">
+    <row r="15" ht="16.5" spans="1:3">
+      <c r="A15" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="15" t="s">
+      <c r="B15" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="16" ht="16.5">
-      <c r="A16" s="15" t="s">
+    <row r="16" ht="16.5" spans="1:3">
+      <c r="A16" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="15" t="s">
+      <c r="B16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="17" ht="16.5">
-      <c r="A17" s="15" t="s">
+    <row r="17" ht="16.5" spans="1:3">
+      <c r="A17" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="15" t="s">
+      <c r="B17" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="18" ht="16.5">
-      <c r="A18" s="15" t="s">
+    <row r="18" ht="16.5" spans="1:3">
+      <c r="A18" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" s="15" t="s">
+      <c r="B18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="19" ht="16.5">
-      <c r="A19" s="15" t="s">
+    <row r="19" ht="16.5" spans="1:3">
+      <c r="A19" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" s="15" t="s">
+      <c r="B19" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="20" ht="16.5">
-      <c r="A20" s="15" t="s">
+    <row r="20" ht="16.5" spans="1:3">
+      <c r="A20" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" s="15" t="s">
+      <c r="B20" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="21" ht="16.5">
-      <c r="A21" s="15" t="s">
+    <row r="21" ht="16.5" spans="1:3">
+      <c r="A21" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C21" s="15" t="s">
+      <c r="B21" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="22" ht="16.5">
-      <c r="A22" s="15" t="s">
+    <row r="22" ht="16.5" spans="1:3">
+      <c r="A22" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C22" s="15" t="s">
+      <c r="B22" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="23" ht="16.5">
-      <c r="A23" s="15" t="s">
+    <row r="23" ht="16.5" spans="1:3">
+      <c r="A23" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B23" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C23" s="15" t="s">
+      <c r="B23" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="24" ht="16.5">
-      <c r="A24" s="15" t="s">
+    <row r="24" ht="16.5" spans="1:3">
+      <c r="A24" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C24" s="15" t="s">
+      <c r="B24" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="25" ht="16.5">
-      <c r="A25" s="15" t="s">
+    <row r="25" ht="16.5" spans="1:3">
+      <c r="A25" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C25" s="15" t="s">
+      <c r="B25" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="26" ht="16.5">
-      <c r="A26" s="15" t="s">
+    <row r="26" ht="16.5" spans="1:3">
+      <c r="A26" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B26" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C26" s="15" t="s">
+      <c r="B26" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="27" ht="16.5">
-      <c r="A27" s="15" t="s">
+    <row r="27" ht="16.5" spans="1:3">
+      <c r="A27" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C27" s="15" t="s">
+      <c r="B27" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="28" ht="16.5">
-      <c r="A28" s="15" t="s">
+    <row r="28" ht="16.5" spans="1:3">
+      <c r="A28" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C28" s="15" t="s">
+      <c r="B28" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="29" ht="16.5">
-      <c r="A29" s="15" t="s">
+    <row r="29" ht="16.5" spans="1:3">
+      <c r="A29" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B29" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C29" s="15" t="s">
+      <c r="B29" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="30" ht="16.5">
-      <c r="A30" s="15" t="s">
+    <row r="30" ht="16.5" spans="1:3">
+      <c r="A30" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C30" s="15" t="s">
+      <c r="B30" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="31" ht="16.5">
-      <c r="A31" s="15" t="s">
+    <row r="31" ht="16.5" spans="1:3">
+      <c r="A31" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C31" s="15" t="s">
+      <c r="B31" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="32" ht="16.5">
-      <c r="A32" s="15" t="s">
+    <row r="32" ht="16.5" spans="1:3">
+      <c r="A32" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B32" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C32" s="15" t="s">
+      <c r="B32" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="33" ht="16.5">
-      <c r="A33" s="15" t="s">
+    <row r="33" ht="16.5" spans="1:3">
+      <c r="A33" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B33" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C33" s="15" t="s">
+      <c r="B33" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="34" ht="16.5">
-      <c r="A34" s="15" t="s">
+    <row r="34" ht="16.5" spans="1:3">
+      <c r="A34" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B34" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C34" s="15" t="s">
+      <c r="B34" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="35" ht="16.5">
-      <c r="A35" s="15" t="s">
+    <row r="35" ht="16.5" spans="1:3">
+      <c r="A35" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B35" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C35" s="15" t="s">
+      <c r="B35" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="36" ht="16.5">
-      <c r="A36" s="15" t="s">
+    <row r="36" ht="16.5" spans="1:3">
+      <c r="A36" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B36" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C36" s="15" t="s">
+      <c r="B36" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="37" ht="16.5">
-      <c r="A37" s="15" t="s">
+    <row r="37" ht="16.5" spans="1:3">
+      <c r="A37" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B37" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C37" s="15" t="s">
+      <c r="B37" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="38" ht="16.5">
-      <c r="A38" s="15" t="s">
+    <row r="38" ht="16.5" spans="1:3">
+      <c r="A38" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B38" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C38" s="15" t="s">
+      <c r="B38" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="39" ht="16.5">
-      <c r="A39" s="15" t="s">
+    <row r="39" ht="16.5" spans="1:3">
+      <c r="A39" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B39" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C39" s="15" t="s">
+      <c r="B39" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="40" ht="16.5">
-      <c r="A40" s="15" t="s">
+    <row r="40" ht="16.5" spans="1:3">
+      <c r="A40" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B40" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C40" s="15" t="s">
+      <c r="B40" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="41" ht="16.5">
-      <c r="A41" s="15" t="s">
+    <row r="41" ht="16.5" spans="1:3">
+      <c r="A41" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B41" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C41" s="15" t="s">
+      <c r="B41" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="42" ht="16.5">
-      <c r="A42" s="15" t="s">
+    <row r="42" ht="16.5" spans="1:3">
+      <c r="A42" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B42" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C42" s="15" t="s">
+      <c r="B42" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="43" ht="16.5">
-      <c r="A43" s="15" t="s">
+    <row r="43" ht="16.5" spans="1:3">
+      <c r="A43" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B43" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C43" s="15" t="s">
+      <c r="B43" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="44" ht="16.5">
-      <c r="A44" s="15" t="s">
+    <row r="44" ht="16.5" spans="1:3">
+      <c r="A44" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B44" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C44" s="15" t="s">
+      <c r="B44" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="45" ht="16.5">
-      <c r="A45" s="15" t="s">
+    <row r="45" ht="16.5" spans="1:3">
+      <c r="A45" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B45" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C45" s="15" t="s">
+      <c r="B45" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="46" ht="16.5">
-      <c r="A46" s="15" t="s">
+    <row r="46" ht="16.5" spans="1:3">
+      <c r="A46" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B46" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C46" s="15" t="s">
+      <c r="B46" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="47" ht="16.5">
-      <c r="A47" s="15" t="s">
+    <row r="47" ht="16.5" spans="1:3">
+      <c r="A47" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B47" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C47" s="15" t="s">
+      <c r="B47" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="48" ht="16.5">
-      <c r="A48" s="15" t="s">
+    <row r="48" ht="16.5" spans="1:3">
+      <c r="A48" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B48" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C48" s="15" t="s">
+      <c r="B48" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="49" ht="16.5">
-      <c r="A49" s="15" t="s">
+    <row r="49" ht="16.5" spans="1:3">
+      <c r="A49" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B49" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C49" s="15" t="s">
+      <c r="B49" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C49" s="2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="50" ht="16.5">
-      <c r="A50" s="15" t="s">
+    <row r="50" ht="16.5" spans="1:3">
+      <c r="A50" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B50" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C50" s="15" t="s">
+      <c r="B50" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C50" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="51" ht="16.5">
-      <c r="A51" s="15" t="s">
+    <row r="51" ht="16.5" spans="1:3">
+      <c r="A51" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B51" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C51" s="15" t="s">
+      <c r="B51" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="52" ht="16.5">
-      <c r="A52" s="15" t="s">
+    <row r="52" ht="16.5" spans="1:3">
+      <c r="A52" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B52" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C52" s="15" t="s">
+      <c r="B52" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C52" s="2" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="53" ht="16.5">
-      <c r="A53" s="15" t="s">
+    <row r="53" ht="16.5" spans="1:3">
+      <c r="A53" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B53" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C53" s="15" t="s">
+      <c r="B53" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C53" s="2" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="54" ht="16.5">
-      <c r="A54" s="15" t="s">
+    <row r="54" ht="16.5" spans="1:3">
+      <c r="A54" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B54" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C54" s="15" t="s">
+      <c r="B54" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C54" s="2" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="55" ht="16.5">
-      <c r="A55" s="15" t="s">
+    <row r="55" ht="16.5" spans="1:3">
+      <c r="A55" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B55" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C55" s="15" t="s">
+      <c r="B55" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C55" s="2" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="56" ht="16.5">
-      <c r="A56" s="15" t="s">
+    <row r="56" ht="16.5" spans="1:3">
+      <c r="A56" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B56" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C56" s="15" t="s">
+      <c r="B56" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C56" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="57" ht="16.5">
-      <c r="A57" s="15" t="s">
+    <row r="57" ht="16.5" spans="1:3">
+      <c r="A57" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B57" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C57" s="15" t="s">
+      <c r="B57" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C57" s="2" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="58" ht="16.5">
-      <c r="A58" s="15" t="s">
+    <row r="58" ht="16.5" spans="1:3">
+      <c r="A58" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B58" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C58" s="15" t="s">
+      <c r="B58" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C58" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="59" ht="16.5">
-      <c r="A59" s="15" t="s">
+    <row r="59" ht="16.5" spans="1:3">
+      <c r="A59" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B59" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C59" s="15" t="s">
+      <c r="B59" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C59" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="60" ht="16.5">
-      <c r="A60" s="15" t="s">
+    <row r="60" ht="16.5" spans="1:3">
+      <c r="A60" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B60" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C60" s="15" t="s">
+      <c r="B60" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="61" ht="16.5">
-      <c r="A61" s="15" t="s">
+    <row r="61" ht="16.5" spans="1:3">
+      <c r="A61" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B61" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C61" s="15" t="s">
+      <c r="B61" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C61" s="2" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="62" ht="16.5">
-      <c r="A62" s="15" t="s">
+    <row r="62" ht="16.5" spans="1:3">
+      <c r="A62" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B62" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C62" s="15" t="s">
+      <c r="B62" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C62" s="2" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="63" ht="16.5">
-      <c r="A63" s="15" t="s">
+    <row r="63" ht="16.5" spans="1:3">
+      <c r="A63" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B63" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C63" s="15" t="s">
+      <c r="B63" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C63" s="2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="64" ht="16.5">
-      <c r="A64" s="15" t="s">
+    <row r="64" ht="16.5" spans="1:3">
+      <c r="A64" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B64" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C64" s="15" t="s">
+      <c r="B64" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C64" s="2" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="65" ht="16.5">
-      <c r="A65" s="15" t="s">
+    <row r="65" ht="16.5" spans="1:3">
+      <c r="A65" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B65" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C65" s="15" t="s">
+      <c r="B65" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C65" s="2" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="66" ht="16.5">
-      <c r="A66" s="15" t="s">
+    <row r="66" ht="16.5" spans="1:3">
+      <c r="A66" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B66" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C66" s="15" t="s">
+      <c r="B66" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C66" s="2" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="67" ht="16.5">
-      <c r="A67" s="15" t="s">
+    <row r="67" ht="16.5" spans="1:3">
+      <c r="A67" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B67" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C67" s="15" t="s">
+      <c r="B67" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C67" s="2" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="68" ht="16.5">
-      <c r="A68" s="15" t="s">
+    <row r="68" ht="16.5" spans="1:3">
+      <c r="A68" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B68" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C68" s="15" t="s">
+      <c r="B68" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C68" s="2" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="69" ht="16.5">
-      <c r="A69" s="15" t="s">
+    <row r="69" ht="16.5" spans="1:3">
+      <c r="A69" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B69" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C69" s="15" t="s">
+      <c r="B69" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C69" s="2" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="70" ht="16.5">
-      <c r="A70" s="15" t="s">
+    <row r="70" ht="16.5" spans="1:3">
+      <c r="A70" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B70" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C70" s="15" t="s">
+      <c r="B70" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C70" s="2" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="71" ht="16.5">
-      <c r="A71" s="15" t="s">
+    <row r="71" ht="16.5" spans="1:3">
+      <c r="A71" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B71" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C71" s="15" t="s">
+      <c r="B71" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C71" s="2" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="72" ht="16.5">
-      <c r="A72" s="15" t="s">
+    <row r="72" ht="16.5" spans="1:3">
+      <c r="A72" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B72" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C72" s="15" t="s">
+      <c r="B72" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C72" s="2" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="73" ht="16.5">
-      <c r="A73" s="15" t="s">
+    <row r="73" ht="16.5" spans="1:3">
+      <c r="A73" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B73" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C73" s="15" t="s">
+      <c r="B73" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C73" s="2" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="74" ht="16.5">
-      <c r="A74" s="15" t="s">
+    <row r="74" ht="16.5" spans="1:3">
+      <c r="A74" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B74" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C74" s="15" t="s">
+      <c r="B74" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C74" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="75" ht="16.5">
-      <c r="A75" s="15" t="s">
+    <row r="75" ht="16.5" spans="1:3">
+      <c r="A75" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B75" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C75" s="15" t="s">
+      <c r="B75" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C75" s="2" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="76" ht="16.5">
-      <c r="A76" s="15" t="s">
+    <row r="76" ht="16.5" spans="1:3">
+      <c r="A76" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B76" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C76" s="15" t="s">
+      <c r="B76" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C76" s="2" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="77" ht="16.5">
-      <c r="A77" s="15" t="s">
+    <row r="77" ht="16.5" spans="1:3">
+      <c r="A77" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B77" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C77" s="15" t="s">
+      <c r="B77" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C77" s="2" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="78" ht="16.5">
-      <c r="A78" s="15" t="s">
+    <row r="78" ht="16.5" spans="1:3">
+      <c r="A78" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B78" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C78" s="15" t="s">
+      <c r="B78" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C78" s="2" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="79" ht="16.5">
-      <c r="A79" s="15" t="s">
+    <row r="79" ht="16.5" spans="1:3">
+      <c r="A79" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B79" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C79" s="15" t="s">
+      <c r="B79" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C79" s="2" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="80" ht="16.5">
-      <c r="A80" s="15" t="s">
+    <row r="80" ht="16.5" spans="1:3">
+      <c r="A80" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B80" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C80" s="15" t="s">
+      <c r="B80" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C80" s="2" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="81" ht="16.5">
-      <c r="A81" s="15" t="s">
+    <row r="81" ht="16.5" spans="1:3">
+      <c r="A81" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B81" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C81" s="15" t="s">
+      <c r="B81" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C81" s="2" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="82" ht="16.5">
-      <c r="A82" s="15" t="s">
+    <row r="82" ht="16.5" spans="1:3">
+      <c r="A82" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B82" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C82" s="15" t="s">
+      <c r="B82" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C82" s="2" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="83" ht="16.5">
-      <c r="A83" s="15" t="s">
+    <row r="83" ht="16.5" spans="1:3">
+      <c r="A83" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B83" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C83" s="15" t="s">
+      <c r="B83" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C83" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="84" ht="16.5">
-      <c r="A84" s="15" t="s">
+    <row r="84" ht="16.5" spans="1:3">
+      <c r="A84" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B84" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C84" s="15" t="s">
+      <c r="B84" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C84" s="2" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="85" ht="16.5">
-      <c r="A85" s="15" t="s">
+    <row r="85" ht="16.5" spans="1:3">
+      <c r="A85" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B85" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C85" s="15" t="s">
+      <c r="B85" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C85" s="2" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="86" ht="16.5">
-      <c r="A86" s="15" t="s">
+    <row r="86" ht="16.5" spans="1:3">
+      <c r="A86" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B86" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C86" s="15" t="s">
+      <c r="B86" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C86" s="2" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="87" ht="16.5">
-      <c r="A87" s="15" t="s">
+    <row r="87" ht="16.5" spans="1:3">
+      <c r="A87" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B87" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C87" s="15" t="s">
+      <c r="B87" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C87" s="2" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="88" ht="16.5">
-      <c r="A88" s="15" t="s">
+    <row r="88" ht="16.5" spans="1:3">
+      <c r="A88" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B88" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C88" s="15" t="s">
+      <c r="B88" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C88" s="2" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="89" ht="16.5">
-      <c r="A89" s="15" t="s">
+    <row r="89" ht="16.5" spans="1:3">
+      <c r="A89" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B89" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C89" s="15" t="s">
+      <c r="B89" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C89" s="2" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="90" ht="16.5">
-      <c r="A90" s="15" t="s">
+    <row r="90" ht="16.5" spans="1:3">
+      <c r="A90" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B90" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C90" s="15" t="s">
+      <c r="B90" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C90" s="2" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="91" ht="16.5">
-      <c r="A91" s="15" t="s">
+    <row r="91" ht="16.5" spans="1:3">
+      <c r="A91" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B91" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C91" s="15" t="s">
+      <c r="B91" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C91" s="2" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="92" ht="16.5">
-      <c r="A92" s="15" t="s">
+    <row r="92" ht="16.5" spans="1:3">
+      <c r="A92" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B92" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C92" s="15" t="s">
+      <c r="B92" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C92" s="2" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="93" ht="16.5">
-      <c r="A93" s="15" t="s">
+    <row r="93" ht="16.5" spans="1:3">
+      <c r="A93" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B93" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C93" s="15" t="s">
+      <c r="B93" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C93" s="2" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="94" ht="16.5">
-      <c r="A94" s="15" t="s">
+    <row r="94" ht="16.5" spans="1:3">
+      <c r="A94" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B94" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C94" s="15" t="s">
+      <c r="B94" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C94" s="2" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="95" ht="16.5">
-      <c r="A95" s="15" t="s">
+    <row r="95" ht="16.5" spans="1:3">
+      <c r="A95" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B95" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C95" s="15" t="s">
+      <c r="B95" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C95" s="2" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="96" ht="16.5">
-      <c r="A96" s="15" t="s">
+    <row r="96" ht="16.5" spans="1:3">
+      <c r="A96" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B96" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C96" s="15" t="s">
+      <c r="B96" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C96" s="2" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="97" ht="16.5">
-      <c r="A97" s="15" t="s">
+    <row r="97" ht="16.5" spans="1:3">
+      <c r="A97" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B97" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C97" s="15" t="s">
+      <c r="B97" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C97" s="2" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="98" ht="16.5">
-      <c r="A98" s="15" t="s">
+    <row r="98" ht="16.5" spans="1:3">
+      <c r="A98" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B98" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C98" s="15" t="s">
+      <c r="B98" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C98" s="2" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="99" ht="16.5">
-      <c r="A99" s="15" t="s">
+    <row r="99" ht="16.5" spans="1:3">
+      <c r="A99" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B99" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C99" s="15" t="s">
+      <c r="B99" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C99" s="2" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="100" ht="16.5">
-      <c r="A100" s="15" t="s">
+    <row r="100" ht="16.5" spans="1:3">
+      <c r="A100" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B100" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C100" s="15" t="s">
+      <c r="B100" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C100" s="2" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="101" ht="16.5">
-      <c r="A101" s="15" t="s">
+    <row r="101" ht="16.5" spans="1:3">
+      <c r="A101" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B101" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C101" s="15" t="s">
+      <c r="B101" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C101" s="2" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="102" ht="16.5">
-      <c r="A102" s="15" t="s">
+    <row r="102" ht="16.5" spans="1:3">
+      <c r="A102" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B102" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C102" s="15" t="s">
+      <c r="B102" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C102" s="2" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="103" ht="16.5">
-      <c r="A103" s="15" t="s">
+    <row r="103" ht="16.5" spans="1:3">
+      <c r="A103" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B103" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C103" s="15" t="s">
+      <c r="B103" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C103" s="2" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="104" ht="16.5">
-      <c r="A104" s="15" t="s">
+    <row r="104" ht="16.5" spans="1:3">
+      <c r="A104" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B104" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C104" s="15" t="s">
+      <c r="B104" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C104" s="2" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="105" ht="16.5">
-      <c r="A105" s="15" t="s">
+    <row r="105" ht="16.5" spans="1:3">
+      <c r="A105" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B105" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C105" s="15" t="s">
+      <c r="B105" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C105" s="2" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="106" ht="16.5">
-      <c r="A106" s="15" t="s">
+    <row r="106" ht="16.5" spans="1:3">
+      <c r="A106" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B106" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C106" s="15" t="s">
+      <c r="B106" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C106" s="2" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="107" ht="16.5">
-      <c r="A107" s="15" t="s">
+    <row r="107" ht="16.5" spans="1:3">
+      <c r="A107" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B107" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C107" s="15" t="s">
+      <c r="B107" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C107" s="2" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="108" ht="16.5">
-      <c r="A108" s="15" t="s">
+    <row r="108" ht="16.5" spans="1:3">
+      <c r="A108" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B108" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C108" s="15" t="s">
+      <c r="B108" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C108" s="2" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="109" ht="16.5">
-      <c r="A109" s="15" t="s">
+    <row r="109" ht="16.5" spans="1:3">
+      <c r="A109" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B109" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C109" s="15" t="s">
+      <c r="B109" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C109" s="2" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="110" ht="16.5">
-      <c r="A110" s="15" t="s">
+    <row r="110" ht="16.5" spans="1:3">
+      <c r="A110" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B110" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C110" s="15" t="s">
+      <c r="B110" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C110" s="2" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="111" ht="16.5">
-      <c r="A111" s="15" t="s">
+    <row r="111" ht="16.5" spans="1:3">
+      <c r="A111" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B111" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C111" s="15" t="s">
+      <c r="B111" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C111" s="2" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="112" ht="16.5">
-      <c r="A112" s="15" t="s">
+    <row r="112" ht="16.5" spans="1:3">
+      <c r="A112" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B112" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C112" s="15" t="s">
+      <c r="B112" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C112" s="2" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="113" ht="16.5">
-      <c r="A113" s="15" t="s">
+    <row r="113" ht="16.5" spans="1:3">
+      <c r="A113" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B113" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C113" s="15" t="s">
+      <c r="B113" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C113" s="2" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="114" ht="16.5">
-      <c r="A114" s="15" t="s">
+    <row r="114" ht="16.5" spans="1:3">
+      <c r="A114" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B114" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C114" s="15" t="s">
+      <c r="B114" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C114" s="2" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="115" ht="16.5">
-      <c r="A115" s="15" t="s">
+    <row r="115" ht="16.5" spans="1:3">
+      <c r="A115" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="B115" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C115" s="15" t="s">
+      <c r="B115" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C115" s="2" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="116" ht="16.5">
-      <c r="A116" s="15" t="s">
+    <row r="116" ht="16.5" spans="1:3">
+      <c r="A116" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="B116" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C116" s="15" t="s">
+      <c r="B116" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C116" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="117" ht="16.5">
-      <c r="A117" s="15" t="s">
+    <row r="117" ht="16.5" spans="1:3">
+      <c r="A117" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B117" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C117" s="15" t="s">
+      <c r="B117" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C117" s="2" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="118" ht="16.5">
-      <c r="A118" s="15" t="s">
+    <row r="118" ht="16.5" spans="1:3">
+      <c r="A118" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="B118" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C118" s="15" t="s">
+      <c r="B118" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C118" s="2" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="119" ht="16.5">
-      <c r="A119" s="15" t="s">
+    <row r="119" ht="16.5" spans="1:3">
+      <c r="A119" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="B119" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C119" s="15" t="s">
+      <c r="B119" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C119" s="2" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="120" ht="16.5">
-      <c r="A120" s="15" t="s">
+    <row r="120" ht="16.5" spans="1:3">
+      <c r="A120" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="B120" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C120" s="15" t="s">
+      <c r="B120" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C120" s="2" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="121" ht="16.5">
-      <c r="A121" s="15" t="s">
+    <row r="121" ht="16.5" spans="1:3">
+      <c r="A121" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B121" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C121" s="15" t="s">
+      <c r="B121" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C121" s="2" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="122" ht="16.5">
-      <c r="A122" s="15" t="s">
+    <row r="122" ht="16.5" spans="1:3">
+      <c r="A122" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B122" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C122" s="15" t="s">
+      <c r="B122" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C122" s="2" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="123" ht="16.5">
-      <c r="A123" s="15" t="s">
+    <row r="123" ht="16.5" spans="1:3">
+      <c r="A123" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B123" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C123" s="15" t="s">
+      <c r="B123" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C123" s="2" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="124" ht="16.5">
-      <c r="A124" s="15" t="s">
+    <row r="124" ht="16.5" spans="1:3">
+      <c r="A124" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B124" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C124" s="15" t="s">
+      <c r="B124" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C124" s="2" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="125" ht="16.5">
-      <c r="A125" s="15" t="s">
+    <row r="125" ht="16.5" spans="1:3">
+      <c r="A125" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B125" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C125" s="15" t="s">
+      <c r="B125" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C125" s="2" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="126" ht="16.5">
-      <c r="A126" s="15" t="s">
+    <row r="126" ht="16.5" spans="1:3">
+      <c r="A126" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B126" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C126" s="15" t="s">
+      <c r="B126" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C126" s="2" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="127" ht="16.5">
-      <c r="A127" s="15" t="s">
+    <row r="127" ht="16.5" spans="1:3">
+      <c r="A127" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B127" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C127" s="15" t="s">
+      <c r="B127" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C127" s="2" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="128" ht="16.5">
-      <c r="A128" s="15" t="s">
+    <row r="128" ht="16.5" spans="1:3">
+      <c r="A128" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B128" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C128" s="15" t="s">
+      <c r="B128" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C128" s="2" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="129" ht="16.5">
-      <c r="A129" s="15" t="s">
+    <row r="129" ht="16.5" spans="1:3">
+      <c r="A129" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B129" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C129" s="15" t="s">
+      <c r="B129" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C129" s="2" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="130" ht="16.5">
-      <c r="A130" s="15" t="s">
+    <row r="130" ht="16.5" spans="1:3">
+      <c r="A130" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B130" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C130" s="15" t="s">
+      <c r="B130" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C130" s="2" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="131" ht="16.5">
-      <c r="A131" s="15" t="s">
+    <row r="131" ht="16.5" spans="1:3">
+      <c r="A131" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B131" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C131" s="15" t="s">
+      <c r="B131" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C131" s="2" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="132" ht="16.5">
-      <c r="A132" s="15" t="s">
+    <row r="132" ht="16.5" spans="1:3">
+      <c r="A132" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="B132" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C132" s="15" t="s">
+      <c r="B132" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C132" s="2" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="133" ht="16.5">
-      <c r="A133" s="15" t="s">
+    <row r="133" ht="16.5" spans="1:3">
+      <c r="A133" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="B133" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C133" s="15" t="s">
+      <c r="B133" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C133" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="134" ht="16.5">
-      <c r="A134" s="15" t="s">
+    <row r="134" ht="16.5" spans="1:3">
+      <c r="A134" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="B134" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C134" s="15" t="s">
+      <c r="B134" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C134" s="2" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="135" ht="16.5">
-      <c r="A135" s="15" t="s">
+    <row r="135" ht="16.5" spans="1:3">
+      <c r="A135" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B135" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C135" s="15" t="s">
+      <c r="B135" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C135" s="2" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="136" ht="16.5">
-      <c r="A136" s="15" t="s">
+    <row r="136" ht="16.5" spans="1:3">
+      <c r="A136" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="B136" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C136" s="15" t="s">
+      <c r="B136" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C136" s="2" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="137" ht="16.5">
-      <c r="A137" s="15" t="s">
+    <row r="137" ht="16.5" spans="1:3">
+      <c r="A137" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="B137" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C137" s="15" t="s">
+      <c r="B137" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C137" s="2" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="138" ht="16.5">
-      <c r="A138" s="15" t="s">
+    <row r="138" ht="16.5" spans="1:3">
+      <c r="A138" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="B138" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C138" s="15" t="s">
+      <c r="B138" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C138" s="2" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="139" ht="16.5">
-      <c r="A139" s="15" t="s">
+    <row r="139" ht="16.5" spans="1:3">
+      <c r="A139" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="B139" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C139" s="15" t="s">
+      <c r="B139" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C139" s="2" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="140" ht="16.5">
-      <c r="A140" s="15" t="s">
+    <row r="140" ht="16.5" spans="1:3">
+      <c r="A140" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="B140" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C140" s="15" t="s">
+      <c r="B140" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C140" s="2" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="141" ht="16.5">
-      <c r="A141" s="15" t="s">
+    <row r="141" ht="16.5" spans="1:3">
+      <c r="A141" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="B141" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C141" s="15" t="s">
+      <c r="B141" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C141" s="2" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="142" ht="16.5">
-      <c r="A142" s="15" t="s">
+    <row r="142" ht="16.5" spans="1:3">
+      <c r="A142" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="B142" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C142" s="15" t="s">
+      <c r="B142" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C142" s="2" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="143" ht="16.5">
-      <c r="A143" s="15" t="s">
+    <row r="143" ht="16.5" spans="1:3">
+      <c r="A143" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="B143" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C143" s="15" t="s">
+      <c r="B143" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C143" s="2" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="144" ht="16.5">
-      <c r="A144" s="15" t="s">
+    <row r="144" ht="16.5" spans="1:3">
+      <c r="A144" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="B144" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C144" s="15" t="s">
+      <c r="B144" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C144" s="2" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="145" ht="16.5">
-      <c r="A145" s="15" t="s">
+    <row r="145" ht="16.5" spans="1:3">
+      <c r="A145" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="B145" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C145" s="15" t="s">
+      <c r="B145" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C145" s="2" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="146" ht="16.5">
-      <c r="A146" s="15" t="s">
+    <row r="146" ht="16.5" spans="1:3">
+      <c r="A146" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B146" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C146" s="15" t="s">
+      <c r="B146" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C146" s="2" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="147" ht="16.5">
-      <c r="A147" s="15" t="s">
+    <row r="147" ht="16.5" spans="1:3">
+      <c r="A147" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B147" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C147" s="15" t="s">
+      <c r="B147" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C147" s="2" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="148" ht="16.5">
-      <c r="A148" s="15" t="s">
+    <row r="148" ht="16.5" spans="1:3">
+      <c r="A148" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="B148" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C148" s="15" t="s">
+      <c r="B148" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C148" s="2" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="149" ht="16.5">
-      <c r="A149" s="15" t="s">
+    <row r="149" ht="16.5" spans="1:3">
+      <c r="A149" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="B149" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C149" s="15" t="s">
+      <c r="B149" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C149" s="2" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="150" ht="16.5">
-      <c r="A150" s="15" t="s">
+    <row r="150" ht="16.5" spans="1:3">
+      <c r="A150" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="B150" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C150" s="15" t="s">
+      <c r="B150" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C150" s="2" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="151" ht="16.5">
-      <c r="A151" s="15" t="s">
+    <row r="151" ht="16.5" spans="1:3">
+      <c r="A151" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="B151" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C151" s="15" t="s">
+      <c r="B151" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C151" s="2" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="152" ht="16.5">
-      <c r="A152" s="15" t="s">
+    <row r="152" ht="16.5" spans="1:3">
+      <c r="A152" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="B152" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C152" s="15" t="s">
+      <c r="B152" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C152" s="2" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="153" ht="16.5">
-      <c r="A153" s="15" t="s">
+    <row r="153" ht="16.5" spans="1:3">
+      <c r="A153" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="B153" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C153" s="15" t="s">
+      <c r="B153" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C153" s="2" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="154" ht="16.5">
-      <c r="A154" s="15" t="s">
+    <row r="154" ht="16.5" spans="1:3">
+      <c r="A154" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="B154" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C154" s="15" t="s">
+      <c r="B154" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C154" s="2" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="155" ht="16.5">
-      <c r="A155" s="15" t="s">
+    <row r="155" ht="16.5" spans="1:3">
+      <c r="A155" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="B155" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C155" s="15" t="s">
+      <c r="B155" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C155" s="2" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="156" ht="16.5">
-      <c r="A156" s="15" t="s">
+    <row r="156" ht="16.5" spans="1:3">
+      <c r="A156" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="B156" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C156" s="15" t="s">
+      <c r="B156" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C156" s="2" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="157" ht="16.5">
-      <c r="A157" s="15" t="s">
+    <row r="157" ht="16.5" spans="1:3">
+      <c r="A157" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="B157" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C157" s="15" t="s">
+      <c r="B157" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C157" s="2" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="158" ht="16.5">
-      <c r="A158" s="15" t="s">
+    <row r="158" ht="16.5" spans="1:3">
+      <c r="A158" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="B158" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C158" s="15" t="s">
+      <c r="B158" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C158" s="2" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="159" ht="16.5">
-      <c r="A159" s="15" t="s">
+    <row r="159" ht="16.5" spans="1:3">
+      <c r="A159" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="B159" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C159" s="15" t="s">
+      <c r="B159" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C159" s="2" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="160" ht="16.5">
-      <c r="A160" s="15" t="s">
+    <row r="160" ht="16.5" spans="1:3">
+      <c r="A160" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="B160" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C160" s="15" t="s">
+      <c r="B160" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C160" s="2" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="161" ht="16.5">
-      <c r="A161" s="15" t="s">
+    <row r="161" ht="16.5" spans="1:3">
+      <c r="A161" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="B161" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C161" s="15" t="s">
+      <c r="B161" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C161" s="2" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="162" ht="16.5">
-      <c r="B162" s="15"/>
-      <c r="C162" s="15"/>
-    </row>
-    <row r="163" ht="16.5">
-      <c r="B163" s="15"/>
-      <c r="C163" s="15"/>
-    </row>
-    <row r="164" ht="16.5">
-      <c r="B164" s="15"/>
-      <c r="C164" s="15"/>
+    <row r="162" ht="16.5" spans="1:3">
+      <c r="A162" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C162" s="3" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="163" ht="16.5" spans="1:3">
+      <c r="A163" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B163" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C163" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="164" ht="16.5" spans="1:3">
+      <c r="A164" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B164" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C164" s="3" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="165" ht="16.5" spans="1:3">
+      <c r="A165" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B165" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C165" s="3" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="166" ht="16.5" spans="1:3">
+      <c r="A166" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B166" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C166" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="167" ht="16.5" spans="1:3">
+      <c r="A167" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B167" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C167" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="168" ht="16.5" spans="1:3">
+      <c r="A168" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="169" ht="16.5" spans="1:3">
+      <c r="A169" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="170" ht="16.5" spans="1:3">
+      <c r="A170" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="171" ht="16.5" spans="1:3">
+      <c r="A171" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C171" s="5" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="172" ht="16.5" spans="1:3">
+      <c r="A172" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C172" s="3" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="173" ht="16.5" spans="1:3">
+      <c r="A173" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C173" s="3" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="174" ht="16.5" spans="1:3">
+      <c r="A174" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C174" s="3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="175" ht="16.5" spans="1:3">
+      <c r="A175" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C175" s="3" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="176" ht="16.5" spans="1:3">
+      <c r="A176" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C176" s="3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="177" ht="16.5" spans="1:3">
+      <c r="A177" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C177" s="3" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="178" ht="16.5" spans="1:3">
+      <c r="A178" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C178" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="179" ht="16.5" spans="1:3">
+      <c r="A179" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C179" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="180" ht="16.5" spans="1:3">
+      <c r="A180" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C180" s="3" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="181" ht="16.5" spans="1:3">
+      <c r="A181" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C181" s="3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="182" ht="16.5" spans="1:3">
+      <c r="A182" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C182" s="3" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="183" ht="16.5" spans="1:3">
+      <c r="A183" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C183" s="3" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="184" ht="16.5" spans="1:3">
+      <c r="A184" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C184" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="185" ht="16.5" spans="1:3">
+      <c r="A185" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C185" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="186" ht="16.5" spans="1:3">
+      <c r="A186" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C186" s="3" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="187" ht="16.5" spans="1:3">
+      <c r="A187" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C187" s="3" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="188" ht="16.5" spans="1:3">
+      <c r="A188" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C188" s="3" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="189" ht="16.5" spans="1:3">
+      <c r="A189" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C189" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="190" ht="16.5" spans="1:3">
+      <c r="A190" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C190" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="191" ht="16.5" spans="1:3">
+      <c r="A191" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C191" s="3" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="192" ht="16.5" spans="1:3">
+      <c r="A192" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C192" s="3" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="193" ht="16.5" spans="1:3">
+      <c r="A193" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C193" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="194" ht="16.5" spans="1:3">
+      <c r="A194" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C194" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="195" ht="16.5" spans="1:3">
+      <c r="A195" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C195" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="196" ht="16.5" spans="1:3">
+      <c r="A196" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C196" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="197" ht="16.5" spans="1:3">
+      <c r="A197" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C197" s="3" t="s">
+        <v>262</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C156"/>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:C161" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>